--- a/archives/customers/docs/CUSTOMERS_GLOBAL.xlsx
+++ b/archives/customers/docs/CUSTOMERS_GLOBAL.xlsx
@@ -89,7 +89,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:H3"/>
+  <dimension ref="A1:H4"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="10" customWidth="1"/>
@@ -227,7 +227,49 @@
         </is>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" t="inlineStr" s="2">
+        <is>
+          <t>CL-003</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr" s="2">
+        <is>
+          <t>TESTEO</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr" s="2">
+        <is>
+          <t>TESTEA</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr" s="2">
+        <is>
+          <t>test</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr" s="2">
+        <is>
+          <t>test</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr" s="2">
+        <is>
+          <t>test</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr" s="2">
+        <is>
+          <t>test</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr" s="2">
+        <is>
+          <t>inactivo</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:H3"/>
+  <autoFilter ref="A1:H4"/>
 </worksheet>
 </file>